--- a/StructureDefinition-ncpi-condition-summary.xlsx
+++ b/StructureDefinition-ncpi-condition-summary.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -370,7 +370,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -651,7 +651,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -678,7 +678,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -718,7 +718,7 @@
     <t>Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -849,7 +849,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -918,7 +918,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -946,7 +946,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1046,7 +1046,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1135,7 +1135,7 @@
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1148,7 +1148,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|DiagnosticReport|Observation)
+    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|DiagnosticReport|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1173,7 +1173,7 @@
     <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1219,7 +1219,7 @@
     <t>Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1238,7 +1238,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1597,7 +1597,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-condition-summary.xlsx
+++ b/StructureDefinition-ncpi-condition-summary.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-ncpi-condition-summary.xlsx
+++ b/StructureDefinition-ncpi-condition-summary.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-condition-summary.xlsx
+++ b/StructureDefinition-ncpi-condition-summary.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-condition-summary.xlsx
+++ b/StructureDefinition-ncpi-condition-summary.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
